--- a/public/exports/29189455.xlsx
+++ b/public/exports/29189455.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 28A</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600946</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>1095</v>
+        <v>506</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311188283</t>
+          <t xml:space="preserve">311189004</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30A</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,20 +3876,20 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601054</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>400</v>
+        <v>824</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311188287</t>
+          <t xml:space="preserve">311189007</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,20 +3951,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J53">
-        <v>506</v>
+        <v>1064</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189004</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J54">
-        <v>824</v>
+        <v>667</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189007</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4091,30 +4091,30 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J55">
-        <v>1064</v>
+        <v>5980</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,40 +4166,40 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J56">
-        <v>667</v>
+        <v>1337</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 4</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,21 +4260,21 @@
         </is>
       </c>
       <c r="J57">
-        <v>5980</v>
+        <v>400</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4331,11 +4331,11 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J58">
-        <v>1337</v>
+        <v>954</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J59">
-        <v>400</v>
+        <v>957</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4466,40 +4466,40 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Korsbakken 9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">3339512</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>954</v>
+        <v>442</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311200372</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,50 +4541,50 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Savværksvej 5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">403587, 403588</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>957</v>
+        <v>750</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311202307</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4616,40 +4616,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbakken 9</t>
+          <t xml:space="preserve">H I Biesgade 4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339512</t>
+          <t xml:space="preserve">5601067</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J62">
-        <v>442</v>
+        <v>287</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200372</t>
+          <t xml:space="preserve">311203630</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savværksvej 5</t>
+          <t xml:space="preserve">Rugmarken 2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">403587, 403588</t>
+          <t xml:space="preserve">3351204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>750</v>
+        <v>497</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202307</t>
+          <t xml:space="preserve">311206994</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">H I Biesgade 4</t>
+          <t xml:space="preserve">Skolekrogen 2A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,30 +4776,30 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601067</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64">
-        <v>287</v>
+        <v>3982</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203630</t>
+          <t xml:space="preserve">311206964</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 2</t>
+          <t xml:space="preserve">Nyvangsvej 8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351204</t>
+          <t xml:space="preserve">3356564</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>497</v>
+        <v>403</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206994</t>
+          <t xml:space="preserve">311207916</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekrogen 2A</t>
+          <t xml:space="preserve">Daniavej 40</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">4078307</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>3982</v>
+        <v>277</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206964</t>
+          <t xml:space="preserve">311212626</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangsvej 8</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356564</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,11 +5010,11 @@
         </is>
       </c>
       <c r="J67">
-        <v>403</v>
+        <v>543</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207916</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,30 +5066,30 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniavej 40</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078307</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212626</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J69">
-        <v>543</v>
+        <v>663</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Bluhmesgade 19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">3350443</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>418</v>
+        <v>1768</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311246240</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,30 +5291,30 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Digtervænget 46</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">5607088</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>663</v>
+        <v>538</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311248868</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluhmesgade 19</t>
+          <t xml:space="preserve">Gl Hobrovej 3A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3350443</t>
+          <t xml:space="preserve">8038852</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>1768</v>
+        <v>520</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246240</t>
+          <t xml:space="preserve">311248873</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digtervænget 46</t>
+          <t xml:space="preserve">Korsgade 2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607088</t>
+          <t xml:space="preserve">5600985</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>538</v>
+        <v>2360</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248868</t>
+          <t xml:space="preserve">311248882</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hobrovej 3A</t>
+          <t xml:space="preserve">Nordre Kajgade 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038852</t>
+          <t xml:space="preserve">5600836</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,11 +5535,11 @@
         </is>
       </c>
       <c r="J74">
-        <v>520</v>
+        <v>850</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248873</t>
+          <t xml:space="preserve">311248866</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 2</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600985</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>2360</v>
+        <v>733</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248882</t>
+          <t xml:space="preserve">311256463</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600836</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J76">
-        <v>850</v>
+        <v>666</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248866</t>
+          <t xml:space="preserve">311258677</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Rørholmsgade 8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5601048</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="J77">
-        <v>733</v>
+        <v>488</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256463</t>
+          <t xml:space="preserve">311259494</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Fjordgade 12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">5601049</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>666</v>
+        <v>512</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258677</t>
+          <t xml:space="preserve">311261189</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørholmsgade 8</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601048</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="J79">
-        <v>488</v>
+        <v>1986</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259494</t>
+          <t xml:space="preserve">311261205</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 12</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601049</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261189</t>
+          <t xml:space="preserve">311261207</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Sjællandsvej 15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5601328</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>1986</v>
+        <v>1380</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261205</t>
+          <t xml:space="preserve">311261221</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,30 +6116,30 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>444</v>
+        <v>556</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261207</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsvej 15</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,20 +6201,20 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601328</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J83">
-        <v>1380</v>
+        <v>906</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261221</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Teglgade 6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5605653</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J84">
-        <v>556</v>
+        <v>621</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311261137</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>906</v>
+        <v>1994</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgade 6</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605653</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>621</v>
+        <v>757</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261137</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J87">
-        <v>1994</v>
+        <v>1368</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J88">
-        <v>757</v>
+        <v>2016</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J89">
-        <v>1368</v>
+        <v>540</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6731,11 +6731,11 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J90">
-        <v>2016</v>
+        <v>1876</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>540</v>
+        <v>834</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,30 +6866,30 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J92">
-        <v>1876</v>
+        <v>1326</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J93">
-        <v>834</v>
+        <v>1670</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286484</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,30 +7016,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
-        <v>1326</v>
+        <v>2252</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286483</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 19</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,20 +7101,20 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>1670</v>
+        <v>401</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286484</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J96">
-        <v>2252</v>
+        <v>401</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286483</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J97">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J98">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J99">
-        <v>401</v>
+        <v>640</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J100">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7556,15 +7556,15 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J101">
-        <v>640</v>
+        <v>296</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311286481</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">8379978</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>354</v>
+        <v>11962</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311288954</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Fayesgade 14A</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,20 +7701,20 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>296</v>
+        <v>1500</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286481</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,30 +7766,30 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Fayesgade 14B</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8379978</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J104">
-        <v>11962</v>
+        <v>2442</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288954</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14A</t>
+          <t xml:space="preserve">Fayesgade 14D</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7856,11 +7856,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J105">
-        <v>1500</v>
+        <v>740</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14B</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J106">
-        <v>2442</v>
+        <v>1229</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,30 +7991,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14D</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J107">
-        <v>740</v>
+        <v>1980</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>1229</v>
+        <v>1065</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J109">
-        <v>1980</v>
+        <v>535</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J110">
-        <v>1065</v>
+        <v>535</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8306,11 +8306,11 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J111">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Ålborgvej 17A</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3357310</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>535</v>
+        <v>309</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311301379</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-07</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,30 +8441,30 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Tempovej 1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3356517</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>377</v>
+        <v>3384</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311303211</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 17A</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357310</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>309</v>
+        <v>777</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301379</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-07</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 1</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356517</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J115">
-        <v>3384</v>
+        <v>689</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303211</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Sverigesvej 3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">8516334</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>777</v>
+        <v>2329</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311307590</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,30 +8741,30 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Timandsvej 25A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J117">
-        <v>689</v>
+        <v>3913</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311317939</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 3</t>
+          <t xml:space="preserve">Timandsvej 25D</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8516334</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J118">
-        <v>2329</v>
+        <v>546</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307590</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25A</t>
+          <t xml:space="preserve">Timandsvej 25E</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J119">
-        <v>3913</v>
+        <v>546</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317939</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25D</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>546</v>
+        <v>297</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311319914</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25E</t>
+          <t xml:space="preserve">Oxendalen 15B</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7996792</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311320212</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">403144</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>297</v>
+        <v>2635</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319914</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15B</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7996792</t>
+          <t xml:space="preserve">403144, 403145</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J123">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320212</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9276,16 +9276,16 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144</t>
+          <t xml:space="preserve">403145</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J124">
-        <v>2635</v>
+        <v>462</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,20 +9351,20 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144, 403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>612</v>
+        <v>5917</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J126">
-        <v>462</v>
+        <v>1420</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>5917</v>
+        <v>960</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311323471</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Bernadottegården 67</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J128">
-        <v>1420</v>
+        <v>252</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Bernadottegården 72</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J129">
-        <v>960</v>
+        <v>252</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323471</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 67</t>
+          <t xml:space="preserve">Bernadottegården 75</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J130">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 72</t>
+          <t xml:space="preserve">Bernadottegården 80</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J131">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 75</t>
+          <t xml:space="preserve">Bernadottegården 83</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J132">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 80</t>
+          <t xml:space="preserve">Bernadottegården 94</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9956,15 +9956,15 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>252</v>
+        <v>5059</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311324163</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,40 +10016,40 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 83</t>
+          <t xml:space="preserve">Edderupvej 3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">4078847</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J134">
-        <v>252</v>
+        <v>802</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311329619</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 94</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J135">
-        <v>5059</v>
+        <v>709</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324163</t>
+          <t xml:space="preserve">311340955</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edderupvej 3</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,30 +10176,30 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078847</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J136">
-        <v>802</v>
+        <v>450</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329619</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10256,15 +10256,15 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J137">
-        <v>709</v>
+        <v>450</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340955</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J138">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J139">
@@ -10466,40 +10466,40 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Skolebakken 4B</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">751527, 4089217</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311382849</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,40 +10541,40 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311499497</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,40 +10616,40 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 4B</t>
+          <t xml:space="preserve">Solvej 10</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">751527, 4089217</t>
+          <t xml:space="preserve">1808922</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J142">
-        <v>268</v>
+        <v>1431</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382849</t>
+          <t xml:space="preserve">311574350</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Hus Check ApS</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Skivevej 27</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,30 +10701,30 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">405931, 100798376</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J143">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499497</t>
+          <t xml:space="preserve">311609330</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,40 +10766,40 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvej 10</t>
+          <t xml:space="preserve">Østergade 21</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808922</t>
+          <t xml:space="preserve">403157, 403158</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>1431</v>
+        <v>501</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574350</t>
+          <t xml:space="preserve">311627846</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus Check ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 27</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">405931, 100798376</t>
+          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>293</v>
+        <v>5995</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609330</t>
+          <t xml:space="preserve">311646437</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 21</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">403157, 403158</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,21 +10935,21 @@
         </is>
       </c>
       <c r="J146">
-        <v>501</v>
+        <v>391</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627846</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,40 +10991,40 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J147">
-        <v>5995</v>
+        <v>925</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646437</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J148">
-        <v>391</v>
+        <v>2948</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J150">
-        <v>2948</v>
+        <v>451</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J151">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11366,40 +11366,40 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Himmerlandsgade 9</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">8603975</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>451</v>
+        <v>3721</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311670894</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Håndværkerparken 2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5602463</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>825</v>
+        <v>586</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311688591</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,30 +11516,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsgade 9</t>
+          <t xml:space="preserve">Søndre Ringvej 11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603975</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J154">
-        <v>3721</v>
+        <v>341</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670894</t>
+          <t xml:space="preserve">311688585</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværkerparken 2</t>
+          <t xml:space="preserve">Adelgade 30B</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602463</t>
+          <t xml:space="preserve">5601052</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,21 +11610,21 @@
         </is>
       </c>
       <c r="J155">
-        <v>586</v>
+        <v>638</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688591</t>
+          <t xml:space="preserve">311790164</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 11</t>
+          <t xml:space="preserve">Søndre Kajgade 18A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,30 +11676,30 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5600779, 100891198</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>341</v>
+        <v>1062</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688585</t>
+          <t xml:space="preserve">311790163</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,30 +11741,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30B</t>
+          <t xml:space="preserve">Hvarrevej 19</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601052</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J157">
-        <v>638</v>
+        <v>315</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790164</t>
+          <t xml:space="preserve">311871713</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 18A</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600779, 100891198</t>
+          <t xml:space="preserve">5605751</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>1062</v>
+        <v>357</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790163</t>
+          <t xml:space="preserve">311887008</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 19</t>
+          <t xml:space="preserve">Stadionvej 9A</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">100024816</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871713</t>
+          <t xml:space="preserve">311887007</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Gl Visborgvej 21</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605751</t>
+          <t xml:space="preserve">3356303</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>357</v>
+        <v>510</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887008</t>
+          <t xml:space="preserve">311891993</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-01</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9A</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024816</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J161">
-        <v>339</v>
+        <v>468</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887007</t>
+          <t xml:space="preserve">311896233</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Visborgvej 21</t>
+          <t xml:space="preserve">Døstrupvej 33A</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356303</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>510</v>
+        <v>659</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311891993</t>
+          <t xml:space="preserve">311896228</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-01</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 21</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">100036624</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>468</v>
+        <v>1670</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896233</t>
+          <t xml:space="preserve">311898865</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33A</t>
+          <t xml:space="preserve">Kirketoften 5</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">5602982</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>659</v>
+        <v>2050</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896228</t>
+          <t xml:space="preserve">311898863</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 21</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036624</t>
+          <t xml:space="preserve">3355780</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>1670</v>
+        <v>2199</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898865</t>
+          <t xml:space="preserve">311899310</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-06</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 5</t>
+          <t xml:space="preserve">Christiansgade 10</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602982</t>
+          <t xml:space="preserve">5600572</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>2050</v>
+        <v>881</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898863</t>
+          <t xml:space="preserve">311903717</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,30 +12491,30 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355780</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J167">
-        <v>2199</v>
+        <v>786</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899310</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-06</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 10</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600572</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J168">
-        <v>881</v>
+        <v>369</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903717</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J169">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J170">
-        <v>369</v>
+        <v>2989</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12806,11 +12806,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J171">
-        <v>770</v>
+        <v>1421</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J172">
-        <v>2989</v>
+        <v>479</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Gettrupvej 3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7007800</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J173">
-        <v>1421</v>
+        <v>1127</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918912</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Ulstrupvej 3C</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,20 +13026,20 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7934937</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>479</v>
+        <v>635</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918911</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gettrupvej 3</t>
+          <t xml:space="preserve">Adelgade 28A</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007800</t>
+          <t xml:space="preserve">5600946</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>1127</v>
+        <v>1095</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918912</t>
+          <t xml:space="preserve">311925680</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3C</t>
+          <t xml:space="preserve">Adelgade 30A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7934937</t>
+          <t xml:space="preserve">5601054</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>635</v>
+        <v>400</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918911</t>
+          <t xml:space="preserve">311925679</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">

--- a/public/exports/29189455.xlsx
+++ b/public/exports/29189455.xlsx
@@ -3416,30 +3416,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4077985</t>
+          <t xml:space="preserve">7864866</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J46">
-        <v>2226</v>
+        <v>360</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179221</t>
+          <t xml:space="preserve">311181429</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-06-07</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Kirkevej 23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J47">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 23</t>
+          <t xml:space="preserve">Kirkevej 9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3581,15 +3581,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>360</v>
+        <v>2671</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181429</t>
+          <t xml:space="preserve">311181419</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,30 +3641,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 9</t>
+          <t xml:space="preserve">Kærvej 30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7864866</t>
+          <t xml:space="preserve">8043516</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J49">
-        <v>2671</v>
+        <v>1366</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181419</t>
+          <t xml:space="preserve">311184922</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-07</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 30</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043516</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>1366</v>
+        <v>506</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184922</t>
+          <t xml:space="preserve">311189004</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3806,15 +3806,15 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J51">
-        <v>506</v>
+        <v>824</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189004</t>
+          <t xml:space="preserve">311189007</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,20 +3876,20 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J52">
-        <v>824</v>
+        <v>1064</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189007</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3956,11 +3956,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J53">
-        <v>1064</v>
+        <v>667</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,30 +4016,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J54">
-        <v>667</v>
+        <v>5980</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,40 +4091,40 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 4</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J55">
-        <v>5980</v>
+        <v>1337</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J56">
-        <v>1337</v>
+        <v>400</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4256,11 +4256,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J57">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4331,11 +4331,11 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J58">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4391,40 +4391,40 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Korsbakken 9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">3339512</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J59">
-        <v>957</v>
+        <v>442</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311200372</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbakken 9</t>
+          <t xml:space="preserve">Savværksvej 5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339512</t>
+          <t xml:space="preserve">403587, 403588</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>442</v>
+        <v>750</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200372</t>
+          <t xml:space="preserve">311202307</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savværksvej 5</t>
+          <t xml:space="preserve">H I Biesgade 4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,40 +4551,40 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">403587, 403588</t>
+          <t xml:space="preserve">5601067</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J61">
-        <v>750</v>
+        <v>287</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202307</t>
+          <t xml:space="preserve">311203630</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4616,40 +4616,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">H I Biesgade 4</t>
+          <t xml:space="preserve">Rugmarken 2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601067</t>
+          <t xml:space="preserve">3351204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>287</v>
+        <v>497</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203630</t>
+          <t xml:space="preserve">311206994</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 2</t>
+          <t xml:space="preserve">Skolekrogen 2A</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351204</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>497</v>
+        <v>3982</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206994</t>
+          <t xml:space="preserve">311206964</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekrogen 2A</t>
+          <t xml:space="preserve">Nyvangsvej 8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">3356564</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>3982</v>
+        <v>403</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206964</t>
+          <t xml:space="preserve">311207916</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangsvej 8</t>
+          <t xml:space="preserve">Daniavej 40</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356564</t>
+          <t xml:space="preserve">4078307</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>403</v>
+        <v>277</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207916</t>
+          <t xml:space="preserve">311212626</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniavej 40</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078307</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>277</v>
+        <v>543</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212626</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5006,11 +5006,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J68">
-        <v>418</v>
+        <v>663</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Bluhmesgade 19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">3350443</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>663</v>
+        <v>1768</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311246240</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluhmesgade 19</t>
+          <t xml:space="preserve">Digtervænget 46</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3350443</t>
+          <t xml:space="preserve">5607088</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>1768</v>
+        <v>538</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246240</t>
+          <t xml:space="preserve">311248868</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digtervænget 46</t>
+          <t xml:space="preserve">Gl Hobrovej 3A</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607088</t>
+          <t xml:space="preserve">8038852</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248868</t>
+          <t xml:space="preserve">311248873</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hobrovej 3A</t>
+          <t xml:space="preserve">Korsgade 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038852</t>
+          <t xml:space="preserve">5600985</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>520</v>
+        <v>2360</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248873</t>
+          <t xml:space="preserve">311248882</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 2</t>
+          <t xml:space="preserve">Nordre Kajgade 1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600985</t>
+          <t xml:space="preserve">5600836</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>2360</v>
+        <v>850</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248882</t>
+          <t xml:space="preserve">311248866</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600836</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,11 +5535,11 @@
         </is>
       </c>
       <c r="J74">
-        <v>850</v>
+        <v>733</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248866</t>
+          <t xml:space="preserve">311256463</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,30 +5591,30 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J75">
-        <v>733</v>
+        <v>666</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256463</t>
+          <t xml:space="preserve">311258677</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Rørholmsgade 8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,30 +5676,30 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">5601048</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>666</v>
+        <v>488</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258677</t>
+          <t xml:space="preserve">311259494</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørholmsgade 8</t>
+          <t xml:space="preserve">Fjordgade 12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601048</t>
+          <t xml:space="preserve">5601049</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="J77">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259494</t>
+          <t xml:space="preserve">311261189</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 12</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601049</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>512</v>
+        <v>1986</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261189</t>
+          <t xml:space="preserve">311261205</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5906,15 +5906,15 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J79">
-        <v>1986</v>
+        <v>444</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261205</t>
+          <t xml:space="preserve">311261207</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Sjællandsvej 15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5601328</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>444</v>
+        <v>1380</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261207</t>
+          <t xml:space="preserve">311261221</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsvej 15</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601328</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>1380</v>
+        <v>556</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261221</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>556</v>
+        <v>906</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Teglgade 6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5605653</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>906</v>
+        <v>621</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311261137</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgade 6</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605653</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J84">
-        <v>621</v>
+        <v>1994</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261137</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6356,11 +6356,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J85">
-        <v>1994</v>
+        <v>757</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J86">
-        <v>757</v>
+        <v>1368</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J87">
-        <v>1368</v>
+        <v>2016</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J88">
-        <v>2016</v>
+        <v>540</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J89">
-        <v>540</v>
+        <v>1876</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>1876</v>
+        <v>834</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6806,11 +6806,11 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>834</v>
+        <v>1326</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6866,30 +6866,30 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J92">
-        <v>1326</v>
+        <v>1670</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286484</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 19</t>
+          <t xml:space="preserve">Amerikavej 21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6956,15 +6956,15 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J93">
-        <v>1670</v>
+        <v>2252</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286484</t>
+          <t xml:space="preserve">311286483</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>2252</v>
+        <v>401</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286483</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J98">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J99">
-        <v>640</v>
+        <v>354</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7481,15 +7481,15 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J100">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311286481</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7541,30 +7541,30 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">8379978</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>296</v>
+        <v>11962</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286481</t>
+          <t xml:space="preserve">311288954</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,17 +7616,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Fayesgade 14A</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8379978</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>11962</v>
+        <v>1500</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288954</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14A</t>
+          <t xml:space="preserve">Fayesgade 14B</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J103">
-        <v>1500</v>
+        <v>2442</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14B</t>
+          <t xml:space="preserve">Fayesgade 14D</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7781,11 +7781,11 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J104">
-        <v>2442</v>
+        <v>740</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14D</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J105">
-        <v>740</v>
+        <v>1229</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J106">
-        <v>1229</v>
+        <v>1980</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8006,11 +8006,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J107">
-        <v>1980</v>
+        <v>1065</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J108">
-        <v>1065</v>
+        <v>535</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J109">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J110">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Ålborgvej 17A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3357310</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311301379</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-07</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 17A</t>
+          <t xml:space="preserve">Tempovej 1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357310</t>
+          <t xml:space="preserve">3356517</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>309</v>
+        <v>3384</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301379</t>
+          <t xml:space="preserve">311303211</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-07</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 1</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356517</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>3384</v>
+        <v>777</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303211</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J114">
-        <v>777</v>
+        <v>689</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Sverigesvej 3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">8516334</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>689</v>
+        <v>2329</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311307590</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 3</t>
+          <t xml:space="preserve">Timandsvej 25A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8516334</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>2329</v>
+        <v>3913</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307590</t>
+          <t xml:space="preserve">311317939</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25A</t>
+          <t xml:space="preserve">Timandsvej 25D</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8756,15 +8756,15 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J117">
-        <v>3913</v>
+        <v>546</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317939</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25D</t>
+          <t xml:space="preserve">Timandsvej 25E</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J118">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25E</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>546</v>
+        <v>297</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311319914</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Oxendalen 15B</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">7996792</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>297</v>
+        <v>582</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319914</t>
+          <t xml:space="preserve">311320212</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15B</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7996792</t>
+          <t xml:space="preserve">403144</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>582</v>
+        <v>2635</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320212</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9126,16 +9126,16 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144</t>
+          <t xml:space="preserve">403144, 403145</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J122">
-        <v>2635</v>
+        <v>612</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9201,16 +9201,16 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144, 403145</t>
+          <t xml:space="preserve">403145</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J123">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,20 +9276,20 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>462</v>
+        <v>5917</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J125">
-        <v>5917</v>
+        <v>1420</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>1420</v>
+        <v>960</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311323471</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Bernadottegården 67</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J127">
-        <v>960</v>
+        <v>252</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323471</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 67</t>
+          <t xml:space="preserve">Bernadottegården 72</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J128">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 72</t>
+          <t xml:space="preserve">Bernadottegården 75</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J129">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 75</t>
+          <t xml:space="preserve">Bernadottegården 80</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J130">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 80</t>
+          <t xml:space="preserve">Bernadottegården 83</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J131">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 83</t>
+          <t xml:space="preserve">Bernadottegården 94</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9881,15 +9881,15 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>252</v>
+        <v>5059</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311324163</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,40 +9941,40 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 94</t>
+          <t xml:space="preserve">Edderupvej 3</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">4078847</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J133">
-        <v>5059</v>
+        <v>802</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324163</t>
+          <t xml:space="preserve">311329619</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edderupvej 3</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,30 +10026,30 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078847</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>802</v>
+        <v>709</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329619</t>
+          <t xml:space="preserve">311340955</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10106,15 +10106,15 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J135">
-        <v>709</v>
+        <v>450</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340955</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J136">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J137">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J138">
@@ -10391,40 +10391,40 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Skolebakken 4B</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">751527, 4089217</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311382849</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,40 +10466,40 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 4B</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">751527, 4089217</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382849</t>
+          <t xml:space="preserve">311499497</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Solvej 10</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,30 +10551,30 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">1808922</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J141">
-        <v>350</v>
+        <v>1431</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499497</t>
+          <t xml:space="preserve">311574350</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Hus Check ApS</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvej 10</t>
+          <t xml:space="preserve">Skivevej 27</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,30 +10626,30 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808922</t>
+          <t xml:space="preserve">405931, 100798376</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>1431</v>
+        <v>293</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574350</t>
+          <t xml:space="preserve">311609330</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus Check ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 27</t>
+          <t xml:space="preserve">Østergade 21</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">405931, 100798376</t>
+          <t xml:space="preserve">403157, 403158</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>293</v>
+        <v>501</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609330</t>
+          <t xml:space="preserve">311627846</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 21</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">403157, 403158</t>
+          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>501</v>
+        <v>5995</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627846</t>
+          <t xml:space="preserve">311646437</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,21 +10860,21 @@
         </is>
       </c>
       <c r="J145">
-        <v>5995</v>
+        <v>391</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646437</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J146">
-        <v>391</v>
+        <v>925</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J147">
-        <v>925</v>
+        <v>2948</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>2948</v>
+        <v>800</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J149">
-        <v>800</v>
+        <v>451</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J150">
-        <v>451</v>
+        <v>825</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11291,40 +11291,40 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Himmerlandsgade 9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">8603975</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>825</v>
+        <v>3721</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311670894</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,17 +11366,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsgade 9</t>
+          <t xml:space="preserve">Håndværkerparken 2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603975</t>
+          <t xml:space="preserve">5602463</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>3721</v>
+        <v>586</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670894</t>
+          <t xml:space="preserve">311688591</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværkerparken 2</t>
+          <t xml:space="preserve">Søndre Ringvej 11</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,20 +11451,20 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602463</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J153">
-        <v>586</v>
+        <v>341</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688591</t>
+          <t xml:space="preserve">311688585</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 11</t>
+          <t xml:space="preserve">Adelgade 30B</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,30 +11526,30 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5601052</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>341</v>
+        <v>638</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688585</t>
+          <t xml:space="preserve">311790164</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30B</t>
+          <t xml:space="preserve">Søndre Kajgade 18A</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601052</t>
+          <t xml:space="preserve">5600779, 100891198</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>638</v>
+        <v>1062</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790164</t>
+          <t xml:space="preserve">311790163</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 18A</t>
+          <t xml:space="preserve">Hvarrevej 19</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600779, 100891198</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J156">
-        <v>1062</v>
+        <v>315</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790163</t>
+          <t xml:space="preserve">311871713</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,30 +11741,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 19</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">5605751</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871713</t>
+          <t xml:space="preserve">311887008</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Stadionvej 9A</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605751</t>
+          <t xml:space="preserve">100024816</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887008</t>
+          <t xml:space="preserve">311887007</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9A</t>
+          <t xml:space="preserve">Gl Visborgvej 21</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024816</t>
+          <t xml:space="preserve">3356303</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>339</v>
+        <v>510</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887007</t>
+          <t xml:space="preserve">311891993</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-01</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,30 +11966,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Visborgvej 21</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356303</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J160">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311891993</t>
+          <t xml:space="preserve">311896233</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-01</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 33A</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,15 +12056,15 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J161">
-        <v>468</v>
+        <v>659</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896233</t>
+          <t xml:space="preserve">311896228</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33A</t>
+          <t xml:space="preserve">Døstrupvej 21</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">100036624</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>659</v>
+        <v>1670</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896228</t>
+          <t xml:space="preserve">311898865</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 21</t>
+          <t xml:space="preserve">Kirketoften 5</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036624</t>
+          <t xml:space="preserve">5602982</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>1670</v>
+        <v>2050</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898865</t>
+          <t xml:space="preserve">311898863</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 5</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602982</t>
+          <t xml:space="preserve">3355780</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>2050</v>
+        <v>2199</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898863</t>
+          <t xml:space="preserve">311899310</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-06</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Christiansgade 10</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355780</t>
+          <t xml:space="preserve">5600572</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>2199</v>
+        <v>881</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899310</t>
+          <t xml:space="preserve">311903717</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-06</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 10</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600572</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J166">
-        <v>881</v>
+        <v>786</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903717</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J167">
-        <v>786</v>
+        <v>369</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J168">
-        <v>369</v>
+        <v>770</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J169">
-        <v>770</v>
+        <v>2989</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J170">
-        <v>2989</v>
+        <v>1421</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12806,11 +12806,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J171">
-        <v>1421</v>
+        <v>479</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Gettrupvej 3</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7007800</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>479</v>
+        <v>1127</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918912</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gettrupvej 3</t>
+          <t xml:space="preserve">Ulstrupvej 3C</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007800</t>
+          <t xml:space="preserve">7934937</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J173">
-        <v>1127</v>
+        <v>635</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918912</t>
+          <t xml:space="preserve">311918911</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3C</t>
+          <t xml:space="preserve">Adelgade 28A</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">7934937</t>
+          <t xml:space="preserve">5600946</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>635</v>
+        <v>1095</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918911</t>
+          <t xml:space="preserve">311925680</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 28A</t>
+          <t xml:space="preserve">Adelgade 30A</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600946</t>
+          <t xml:space="preserve">5601054</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>1095</v>
+        <v>400</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925680</t>
+          <t xml:space="preserve">311925679</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30A</t>
+          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601054</t>
+          <t xml:space="preserve">4077985</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>400</v>
+        <v>2226</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925679</t>
+          <t xml:space="preserve">311926396</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">

--- a/public/exports/29189455.xlsx
+++ b/public/exports/29189455.xlsx
@@ -1316,26 +1316,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvejen 1</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356242</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J18">
-        <v>460</v>
+        <v>252</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,26 +1391,26 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J19">
-        <v>252</v>
+        <v>388</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,26 +1466,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">751387, 3357680</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J20">
-        <v>388</v>
+        <v>525</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1556,11 +1556,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J21">
-        <v>525</v>
+        <v>699</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1631,11 +1631,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J22">
-        <v>699</v>
+        <v>670</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1706,11 +1706,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J23">
-        <v>670</v>
+        <v>1236</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1781,11 +1781,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J24">
-        <v>1236</v>
+        <v>1874</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1856,11 +1856,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J25">
-        <v>1874</v>
+        <v>820</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J26">
-        <v>820</v>
+        <v>291</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Sverigesvej 1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,16 +2001,16 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">751387, 3357680</t>
+          <t xml:space="preserve">8147317</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J27">
-        <v>291</v>
+        <v>448</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,26 +2066,26 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 1</t>
+          <t xml:space="preserve">Søndre Kajgade 14A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8147317</t>
+          <t xml:space="preserve">751509, 8647765</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J28">
-        <v>448</v>
+        <v>964</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,26 +2141,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 14A</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">751509, 8647765</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>964</v>
+        <v>781</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2216,17 +2216,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Thygeslundvej 9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">751464, 3354738</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="J30">
-        <v>781</v>
+        <v>361</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,26 +2291,26 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygeslundvej 9</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">751464, 3354738</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J31">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Ulstrupvej 3A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,16 +2376,16 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J32">
-        <v>420</v>
+        <v>687</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,45 +2441,45 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3A</t>
+          <t xml:space="preserve">Langerimsvej 3B</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">751602, 3344137</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>687</v>
+        <v>490</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve">100157186</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-04-26</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2516,30 +2516,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langerimsvej 3B</t>
+          <t xml:space="preserve">Bønfeltvej 2D</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">751602, 3344137</t>
+          <t xml:space="preserve">3344709, 100801117</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J34">
-        <v>490</v>
+        <v>377</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">100157186</t>
+          <t xml:space="preserve">200039964</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-26</t>
+          <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bønfeltvej 2D</t>
+          <t xml:space="preserve">Thygeslundvej 9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3344709, 100801117</t>
+          <t xml:space="preserve">751464, 3354738</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="J35">
-        <v>377</v>
+        <v>872</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039964</t>
+          <t xml:space="preserve">200040715</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-28</t>
+          <t xml:space="preserve">2020-11-09</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,40 +2666,40 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygeslundvej 9</t>
+          <t xml:space="preserve">Hjulhusvej 5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">751464, 3354738</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J36">
-        <v>872</v>
+        <v>262</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040715</t>
+          <t xml:space="preserve">200042106</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-09</t>
+          <t xml:space="preserve">2020-12-01</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,40 +2741,40 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 5</t>
+          <t xml:space="preserve">Idrætsvej 15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">751447, 3348690</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>262</v>
+        <v>738</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042106</t>
+          <t xml:space="preserve">200059298</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">Dansk Bygningstermografi</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-01</t>
+          <t xml:space="preserve">2022-05-03</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 15</t>
+          <t xml:space="preserve">Langerimsvej 7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">751447, 3348690</t>
+          <t xml:space="preserve">751474, 3344194</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>738</v>
+        <v>1948</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059298</t>
+          <t xml:space="preserve">200059329</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-03</t>
+          <t xml:space="preserve">2022-05-06</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langerimsvej 7</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,20 +2901,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">751474, 3344194</t>
+          <t xml:space="preserve">751387, 3357680</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J39">
-        <v>1948</v>
+        <v>1398</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059329</t>
+          <t xml:space="preserve">200059504</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-06</t>
+          <t xml:space="preserve">2022-05-12</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2981,11 +2981,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J40">
-        <v>1398</v>
+        <v>253</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Skolemarken 2A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">751387, 3357680</t>
+          <t xml:space="preserve">751290, 8764792</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>253</v>
+        <v>898</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059504</t>
+          <t xml:space="preserve">200060070</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-12</t>
+          <t xml:space="preserve">2022-06-09</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolemarken 2A</t>
+          <t xml:space="preserve">Hvarrevej 6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">751290, 8764792</t>
+          <t xml:space="preserve">751283, 3351340</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J42">
-        <v>898</v>
+        <v>2188</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060070</t>
+          <t xml:space="preserve">200060601</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-09</t>
+          <t xml:space="preserve">2022-06-30</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 6</t>
+          <t xml:space="preserve">Hvarrevej 8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,20 +3201,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">751283, 3351340</t>
+          <t xml:space="preserve">751284, 3351342</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J43">
-        <v>2188</v>
+        <v>1371</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060601</t>
+          <t xml:space="preserve">200060602</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3266,40 +3266,40 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 8</t>
+          <t xml:space="preserve">Kirketoften 6A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">751284, 3351342</t>
+          <t xml:space="preserve">405503, 405504</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>1371</v>
+        <v>2595</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060602</t>
+          <t xml:space="preserve">311178903</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningstermografi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-30</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 6A</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">405503, 405504</t>
+          <t xml:space="preserve">7864866</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J45">
-        <v>2595</v>
+        <v>360</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178903</t>
+          <t xml:space="preserve">311181429</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-07</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Kirkevej 23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J46">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 23</t>
+          <t xml:space="preserve">Kirkevej 9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,15 +3506,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>360</v>
+        <v>2671</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181429</t>
+          <t xml:space="preserve">311181419</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 9</t>
+          <t xml:space="preserve">Kærvej 30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7864866</t>
+          <t xml:space="preserve">8043516</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J48">
-        <v>2671</v>
+        <v>1366</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181419</t>
+          <t xml:space="preserve">311184922</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-07</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 30</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043516</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J49">
-        <v>1366</v>
+        <v>506</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184922</t>
+          <t xml:space="preserve">311189004</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3731,15 +3731,15 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J50">
-        <v>506</v>
+        <v>824</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189004</t>
+          <t xml:space="preserve">311189007</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J51">
-        <v>824</v>
+        <v>1064</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189007</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3881,11 +3881,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J52">
-        <v>1064</v>
+        <v>667</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,30 +3941,30 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J53">
-        <v>667</v>
+        <v>5980</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,40 +4016,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 4</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J54">
-        <v>5980</v>
+        <v>1337</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4106,11 +4106,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J55">
-        <v>1337</v>
+        <v>400</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J56">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4256,11 +4256,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J57">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,40 +4316,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Korsbakken 9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">3339512</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>957</v>
+        <v>442</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311200372</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbakken 9</t>
+          <t xml:space="preserve">Savværksvej 5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339512</t>
+          <t xml:space="preserve">403587, 403588</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>442</v>
+        <v>750</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200372</t>
+          <t xml:space="preserve">311202307</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savværksvej 5</t>
+          <t xml:space="preserve">H I Biesgade 4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,30 +4476,30 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">403587, 403588</t>
+          <t xml:space="preserve">5601067</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>750</v>
+        <v>287</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202307</t>
+          <t xml:space="preserve">311203630</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">H I Biesgade 4</t>
+          <t xml:space="preserve">Skolekrogen 2A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,30 +4551,30 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601067</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>287</v>
+        <v>3982</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203630</t>
+          <t xml:space="preserve">311206964</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 2</t>
+          <t xml:space="preserve">Nyvangsvej 8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351204</t>
+          <t xml:space="preserve">3356564</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>497</v>
+        <v>403</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206994</t>
+          <t xml:space="preserve">311207916</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekrogen 2A</t>
+          <t xml:space="preserve">Daniavej 40</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">4078307</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>3982</v>
+        <v>277</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206964</t>
+          <t xml:space="preserve">311212626</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangsvej 8</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356564</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>403</v>
+        <v>543</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207916</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,30 +4841,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniavej 40</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078307</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J65">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212626</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J66">
-        <v>543</v>
+        <v>663</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Bluhmesgade 19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">3350443</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>418</v>
+        <v>1768</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311246240</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,30 +5066,30 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Digtervænget 46</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">5607088</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>663</v>
+        <v>538</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311248868</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluhmesgade 19</t>
+          <t xml:space="preserve">Gl Hobrovej 3A</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3350443</t>
+          <t xml:space="preserve">8038852</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>1768</v>
+        <v>520</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246240</t>
+          <t xml:space="preserve">311248873</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digtervænget 46</t>
+          <t xml:space="preserve">Korsgade 2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607088</t>
+          <t xml:space="preserve">5600985</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>538</v>
+        <v>2360</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248868</t>
+          <t xml:space="preserve">311248882</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hobrovej 3A</t>
+          <t xml:space="preserve">Nordre Kajgade 1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038852</t>
+          <t xml:space="preserve">5600836</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>520</v>
+        <v>850</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248873</t>
+          <t xml:space="preserve">311248866</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 2</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600985</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>2360</v>
+        <v>733</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248882</t>
+          <t xml:space="preserve">311256463</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600836</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J73">
-        <v>850</v>
+        <v>666</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248866</t>
+          <t xml:space="preserve">311258677</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,17 +5516,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Rørholmsgade 8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5601048</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="J74">
-        <v>733</v>
+        <v>488</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256463</t>
+          <t xml:space="preserve">311259494</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Fjordgade 12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">5601049</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>666</v>
+        <v>512</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258677</t>
+          <t xml:space="preserve">311261189</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørholmsgade 8</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601048</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="J76">
-        <v>488</v>
+        <v>1986</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259494</t>
+          <t xml:space="preserve">311261205</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 12</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601049</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J77">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261189</t>
+          <t xml:space="preserve">311261207</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Sjællandsvej 15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5601328</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>1986</v>
+        <v>1380</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261205</t>
+          <t xml:space="preserve">311261221</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5891,30 +5891,30 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>444</v>
+        <v>556</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261207</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsvej 15</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601328</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>1380</v>
+        <v>906</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261221</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Teglgade 6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5605653</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>556</v>
+        <v>621</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311261137</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,20 +6126,20 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>906</v>
+        <v>1994</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgade 6</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605653</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J83">
-        <v>621</v>
+        <v>757</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261137</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6281,11 +6281,11 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J84">
-        <v>1994</v>
+        <v>1368</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6356,11 +6356,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J85">
-        <v>757</v>
+        <v>2016</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J86">
-        <v>1368</v>
+        <v>540</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J87">
-        <v>2016</v>
+        <v>1876</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J88">
-        <v>540</v>
+        <v>834</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,30 +6641,30 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J89">
-        <v>1876</v>
+        <v>1326</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J90">
-        <v>834</v>
+        <v>1670</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286484</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J91">
-        <v>1326</v>
+        <v>2252</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286483</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 19</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>1670</v>
+        <v>401</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286484</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J93">
-        <v>2252</v>
+        <v>401</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286483</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J95">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7181,11 +7181,11 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J96">
-        <v>401</v>
+        <v>640</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7256,11 +7256,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J97">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7331,15 +7331,15 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J98">
-        <v>640</v>
+        <v>296</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311286481</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">8379978</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>354</v>
+        <v>11962</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311288954</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Fayesgade 14A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>296</v>
+        <v>1500</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286481</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,30 +7541,30 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Fayesgade 14B</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8379978</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J101">
-        <v>11962</v>
+        <v>2442</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288954</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14A</t>
+          <t xml:space="preserve">Fayesgade 14D</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J102">
-        <v>1500</v>
+        <v>740</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7691,30 +7691,30 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14B</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J103">
-        <v>2442</v>
+        <v>1229</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,30 +7766,30 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14D</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J104">
-        <v>740</v>
+        <v>1980</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7856,11 +7856,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J105">
-        <v>1229</v>
+        <v>1065</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7931,11 +7931,11 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J106">
-        <v>1980</v>
+        <v>535</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8006,11 +8006,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J107">
-        <v>1065</v>
+        <v>535</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J108">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Ålborgvej 17A</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3357310</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>535</v>
+        <v>309</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311301379</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-07</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,30 +8216,30 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Tempovej 1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3356517</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>377</v>
+        <v>3384</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311303211</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 17A</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357310</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>309</v>
+        <v>777</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301379</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-07</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 1</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356517</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J112">
-        <v>3384</v>
+        <v>689</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303211</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Sverigesvej 3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">8516334</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>777</v>
+        <v>2329</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311307590</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Timandsvej 25A</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>689</v>
+        <v>3913</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311317939</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 3</t>
+          <t xml:space="preserve">Timandsvej 25D</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8516334</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J115">
-        <v>2329</v>
+        <v>546</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307590</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25A</t>
+          <t xml:space="preserve">Timandsvej 25E</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8681,15 +8681,15 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J116">
-        <v>3913</v>
+        <v>546</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317939</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,30 +8741,30 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25D</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J117">
-        <v>546</v>
+        <v>297</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311319914</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,30 +8816,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25E</t>
+          <t xml:space="preserve">Oxendalen 15B</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7996792</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311320212</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">403144</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>297</v>
+        <v>2635</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319914</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15B</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7996792</t>
+          <t xml:space="preserve">403144, 403145</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320212</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9051,16 +9051,16 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144</t>
+          <t xml:space="preserve">403145</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J121">
-        <v>2635</v>
+        <v>462</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144, 403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>612</v>
+        <v>5917</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J123">
-        <v>462</v>
+        <v>1420</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>5917</v>
+        <v>960</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311323471</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,30 +9341,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Bernadottegården 67</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J125">
-        <v>1420</v>
+        <v>252</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Bernadottegården 72</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J126">
-        <v>960</v>
+        <v>252</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323471</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 67</t>
+          <t xml:space="preserve">Bernadottegården 75</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J127">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 72</t>
+          <t xml:space="preserve">Bernadottegården 80</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J128">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 75</t>
+          <t xml:space="preserve">Bernadottegården 83</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J129">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 80</t>
+          <t xml:space="preserve">Bernadottegården 94</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9731,15 +9731,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>252</v>
+        <v>5059</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311324163</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,40 +9791,40 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 83</t>
+          <t xml:space="preserve">Edderupvej 3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">4078847</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J131">
-        <v>252</v>
+        <v>802</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311329619</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 94</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>5059</v>
+        <v>709</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324163</t>
+          <t xml:space="preserve">311340955</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edderupvej 3</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,30 +9951,30 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078847</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J133">
-        <v>802</v>
+        <v>450</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329619</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10031,15 +10031,15 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J134">
-        <v>709</v>
+        <v>450</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340955</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J135">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J136">
@@ -10241,40 +10241,40 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Skolebakken 4B</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">751527, 4089217</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311382849</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,40 +10316,40 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311499497</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,40 +10391,40 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 4B</t>
+          <t xml:space="preserve">Solvej 10</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">751527, 4089217</t>
+          <t xml:space="preserve">1808922</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J139">
-        <v>268</v>
+        <v>1431</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382849</t>
+          <t xml:space="preserve">311574350</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Hus Check ApS</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Skivevej 27</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,30 +10476,30 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">405931, 100798376</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499497</t>
+          <t xml:space="preserve">311609330</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,40 +10541,40 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvej 10</t>
+          <t xml:space="preserve">Østergade 21</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808922</t>
+          <t xml:space="preserve">403157, 403158</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>1431</v>
+        <v>501</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574350</t>
+          <t xml:space="preserve">311627846</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus Check ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 27</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">405931, 100798376</t>
+          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>293</v>
+        <v>5995</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609330</t>
+          <t xml:space="preserve">311646437</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 21</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">403157, 403158</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="J143">
-        <v>501</v>
+        <v>391</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627846</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,40 +10766,40 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J144">
-        <v>5995</v>
+        <v>925</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646437</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J145">
-        <v>391</v>
+        <v>2948</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J147">
-        <v>2948</v>
+        <v>451</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J148">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11141,40 +11141,40 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Himmerlandsgade 9</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">8603975</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J149">
-        <v>451</v>
+        <v>3721</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311670894</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Håndværkerparken 2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,30 +11226,30 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5602463</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>825</v>
+        <v>586</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311688591</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsgade 9</t>
+          <t xml:space="preserve">Søndre Ringvej 11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603975</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J151">
-        <v>3721</v>
+        <v>341</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670894</t>
+          <t xml:space="preserve">311688585</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværkerparken 2</t>
+          <t xml:space="preserve">Adelgade 30B</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602463</t>
+          <t xml:space="preserve">5601052</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,21 +11385,21 @@
         </is>
       </c>
       <c r="J152">
-        <v>586</v>
+        <v>638</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688591</t>
+          <t xml:space="preserve">311790164</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 11</t>
+          <t xml:space="preserve">Søndre Kajgade 18A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5600779, 100891198</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>341</v>
+        <v>1062</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688585</t>
+          <t xml:space="preserve">311790163</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,30 +11516,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30B</t>
+          <t xml:space="preserve">Hvarrevej 19</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601052</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J154">
-        <v>638</v>
+        <v>315</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790164</t>
+          <t xml:space="preserve">311871713</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 18A</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600779, 100891198</t>
+          <t xml:space="preserve">5605751</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>1062</v>
+        <v>357</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790163</t>
+          <t xml:space="preserve">311887008</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 19</t>
+          <t xml:space="preserve">Stadionvej 9A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">100024816</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871713</t>
+          <t xml:space="preserve">311887007</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Gl Visborgvej 21</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605751</t>
+          <t xml:space="preserve">3356303</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>357</v>
+        <v>510</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887008</t>
+          <t xml:space="preserve">311891993</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-01</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9A</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024816</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J158">
-        <v>339</v>
+        <v>468</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887007</t>
+          <t xml:space="preserve">311896233</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Visborgvej 21</t>
+          <t xml:space="preserve">Døstrupvej 33A</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356303</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J159">
-        <v>510</v>
+        <v>659</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311891993</t>
+          <t xml:space="preserve">311896228</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-01</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 21</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,20 +11976,20 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">100036624</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>468</v>
+        <v>1670</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896233</t>
+          <t xml:space="preserve">311898865</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33A</t>
+          <t xml:space="preserve">Kirketoften 5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">5602982</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J161">
-        <v>659</v>
+        <v>2050</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896228</t>
+          <t xml:space="preserve">311898863</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 21</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036624</t>
+          <t xml:space="preserve">3355780</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>1670</v>
+        <v>2199</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898865</t>
+          <t xml:space="preserve">311899310</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-06</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 5</t>
+          <t xml:space="preserve">Christiansgade 10</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602982</t>
+          <t xml:space="preserve">5600572</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>2050</v>
+        <v>881</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898863</t>
+          <t xml:space="preserve">311903717</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,30 +12266,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355780</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J164">
-        <v>2199</v>
+        <v>786</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899310</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-06</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 10</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600572</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J165">
-        <v>881</v>
+        <v>369</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903717</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J166">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J167">
-        <v>369</v>
+        <v>2989</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J168">
-        <v>770</v>
+        <v>1421</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J169">
-        <v>2989</v>
+        <v>479</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Gettrupvej 3</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7007800</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
-        <v>1421</v>
+        <v>1127</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918912</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Ulstrupvej 3C</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7934937</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>479</v>
+        <v>635</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918911</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gettrupvej 3</t>
+          <t xml:space="preserve">Adelgade 28A</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007800</t>
+          <t xml:space="preserve">5600946</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J172">
-        <v>1127</v>
+        <v>1095</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918912</t>
+          <t xml:space="preserve">311925680</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3C</t>
+          <t xml:space="preserve">Adelgade 30A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7934937</t>
+          <t xml:space="preserve">5601054</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="J173">
-        <v>635</v>
+        <v>400</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918911</t>
+          <t xml:space="preserve">311925679</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 28A</t>
+          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600946</t>
+          <t xml:space="preserve">4077985</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>1095</v>
+        <v>2226</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925680</t>
+          <t xml:space="preserve">311926396</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30A</t>
+          <t xml:space="preserve">Ringvejen 1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601054</t>
+          <t xml:space="preserve">3356242</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J175">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925679</t>
+          <t xml:space="preserve">311930425</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
+          <t xml:space="preserve">Rugmarken 2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4077985</t>
+          <t xml:space="preserve">3351204</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>2226</v>
+        <v>497</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926396</t>
+          <t xml:space="preserve">311930424</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-17</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
